--- a/data/trans_orig/IP07_C14_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C14_2023-Provincia-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han producido situaciones de cyberbulling en su colegio en 2023 (tasa de respuesta: 94,11%)</t>
+          <t>Menores según si se han producido situaciones de cyberbulling en su colegio/instituto en 2023 (tasa de respuesta: 94,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,57 +725,57 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>513</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>513</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>513</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>513</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>513</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>513</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6444</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2583</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13218</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13,51%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,41%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>27,7%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6699</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1409</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14533</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>10,98%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>23,81%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2414</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13429</t>
+          <t>11496</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>13433</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21896</t>
+          <t>21674</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>41269</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>34495</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>45130</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86,49%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>72,3%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,59%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>54337</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>46503</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>59627</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>89,02%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>76,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,69%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>44165</t>
+          <t>30692</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37470</t>
+          <t>26126</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48485</t>
+          <t>33957</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>98502</t>
+          <t>71960</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>90039</t>
+          <t>63660</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>107155</t>
+          <t>77157</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47713</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47713</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47713</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>61036</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>61036</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>61036</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50899</t>
+          <t>37622</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50899</t>
+          <t>37622</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50899</t>
+          <t>37622</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>111935</t>
+          <t>85334</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>111935</t>
+          <t>85334</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>111935</t>
+          <t>85334</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6793</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3682</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10456</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>32,62%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>17,68%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>50,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6355</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3525</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9948</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>31,4%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,42%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>49,15%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11710</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13816</t>
+          <t>13070</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>8283</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18844</t>
+          <t>17996</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,84%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14030</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10367</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>17141</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>67,38%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>49,79%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>82,32%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>13883</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>10290</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>16713</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>68,6%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>50,85%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>82,58%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15380</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11132</t>
+          <t>10140</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18643</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>29264</t>
+          <t>27979</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24236</t>
+          <t>23053</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33879</t>
+          <t>32766</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>79,82%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22842</t>
+          <t>20226</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22842</t>
+          <t>20226</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22842</t>
+          <t>20226</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>43080</t>
+          <t>41049</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>43080</t>
+          <t>41049</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>43080</t>
+          <t>41049</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>492</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>382</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1814,42 +1814,42 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>75,93%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3696</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>18,14%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>712</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3351</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -1862,74 +1862,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16939</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14313</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>82,11%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2486</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>93,85%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2556</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2938</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>87,01%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>24,07%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>19201</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>16163</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>19750</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,22%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>81,84%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -1937,27 +1937,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>21687</t>
+          <t>19496</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19048</t>
+          <t>16673</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2893</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14,26%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1009</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1042</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3291</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,87%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3265</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>6,69%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>22,39%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>580</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3459</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>490</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -2205,74 +2205,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>19670</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>17392</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,97%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>85,74%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>13689</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>11407</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>93,13%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>77,61%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>14532</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>12309</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>15574</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>93,31%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>79,03%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>19402</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>16523</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>19982</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>82,69%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>59</t>
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>33090</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30074</t>
+          <t>31517</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34219</t>
+          <t>35369</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7127</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4116</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>11305</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>39,14%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>22,61%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>62,09%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>4964</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2423</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8295</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>29,5%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>14,4%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>49,31%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>2541</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12625</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>12937</t>
+          <t>12210</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8402</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18698</t>
+          <t>17789</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>49,68%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11081</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6903</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>14092</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>60,86%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>37,91%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>77,39%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>11860</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>8529</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>14401</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>70,5%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>50,69%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>85,6%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11663</t>
+          <t>12518</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7011</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>15059</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>23524</t>
+          <t>23599</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17763</t>
+          <t>18020</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28059</t>
+          <t>27668</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,27%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16824</t>
+          <t>18208</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16824</t>
+          <t>18208</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16824</t>
+          <t>18208</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19636</t>
+          <t>17600</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19636</t>
+          <t>17600</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19636</t>
+          <t>17600</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>36461</t>
+          <t>35809</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>36461</t>
+          <t>35809</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36461</t>
+          <t>35809</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>10121</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>5832</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>15827</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>27,09%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>15,61%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>42,36%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>6146</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2943</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>10093</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>26,52%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>43,54%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15780</t>
+          <t>11228</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>16248</t>
+          <t>16616</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23975</t>
+          <t>23417</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>37,89%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>27238</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>21532</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>31527</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>72,91%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>57,64%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>84,39%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>17034</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>13087</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>20237</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>73,48%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>56,46%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>87,31%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>26379</t>
+          <t>17955</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20701</t>
+          <t>13222</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>31112</t>
+          <t>21196</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>43413</t>
+          <t>45192</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>35686</t>
+          <t>38391</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48766</t>
+          <t>50807</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,2%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>37359</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>37359</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>37359</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>23180</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>23180</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>23180</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>36481</t>
+          <t>24450</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>36481</t>
+          <t>24450</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>36481</t>
+          <t>24450</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>59661</t>
+          <t>61808</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>59661</t>
+          <t>61808</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>59661</t>
+          <t>61808</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>1212</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3480</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>337</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>341</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>61583</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>59315</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>62417</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>94,46%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>68503</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66273</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>69249</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>142898</t>
+          <t>155752</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>140727</t>
+          <t>153735</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>143736</t>
+          <t>156494</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>62795</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>62795</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>62795</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>69586</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>69586</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>69586</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>144110</t>
+          <t>156835</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>144110</t>
+          <t>156835</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>144110</t>
+          <t>156835</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>31593</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>22255</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>42528</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>12,68%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>8,94%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>17,07%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>26548</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>16535</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>36535</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>13,15%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>18,09%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>33400</t>
+          <t>27291</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24269</t>
+          <t>21073</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>46183</t>
+          <t>36454</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>59948</t>
+          <t>58883</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>45397</t>
+          <t>46261</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>73927</t>
+          <t>72535</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>217475</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>206540</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>226813</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>87,32%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>82,93%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>91,06%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>175379</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>165392</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>185392</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>86,85%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>81,91%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>91,81%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>217506</t>
+          <t>161219</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>204723</t>
+          <t>152056</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>226637</t>
+          <t>167437</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>392885</t>
+          <t>378694</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>378906</t>
+          <t>365042</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>407436</t>
+          <t>391316</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,43%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>249068</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>249068</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>249068</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>201927</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>201927</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>201927</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>250906</t>
+          <t>188510</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>250906</t>
+          <t>188510</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>250906</t>
+          <t>188510</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>452833</t>
+          <t>437577</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>452833</t>
+          <t>437577</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>452833</t>
+          <t>437577</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
